--- a/output/pdf_financials_xlsx/KAS.xlsx
+++ b/output/pdf_financials_xlsx/KAS.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.428368</v>
+        <v>1.157409</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.686075</v>
@@ -651,16 +651,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.039266</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.023934</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
     </row>
     <row r="13">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.882086</v>
+        <v>-5.921352</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.213765</v>
+        <v>-2.237699</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.608125</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.555921</v>
+        <v>-3.555928</v>
       </c>
     </row>
     <row r="28">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.882086</v>
+        <v>-5.921352</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.213765</v>
+        <v>-2.237699</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.487813</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.978421</v>
+        <v>-2.978428</v>
       </c>
     </row>
     <row r="30">
@@ -1022,7 +1022,7 @@
         <v>-174882.5047801147</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-314511.1932418162</v>
+        <v>-314511.9324181626</v>
       </c>
     </row>
     <row r="31">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.021683</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003276</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.005108</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.110491</v>
       </c>
     </row>
     <row r="35">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.021683</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003276</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.005108</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.110491</v>
       </c>
     </row>
     <row r="37">
@@ -1347,16 +1347,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.076522</v>
+        <v>2.054839</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.77876</v>
+        <v>3.775484</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.008247000000000001</v>
+        <v>0.003139</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.198973</v>
+        <v>0.08848200000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E228" s="5" t="n">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E233" s="5" t="n">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E236" s="5" t="n">

--- a/output/pdf_financials_xlsx/KAS.xlsx
+++ b/output/pdf_financials_xlsx/KAS.xlsx
@@ -1662,13 +1662,13 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.058074</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.113566</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.321766</v>
       </c>
     </row>
     <row r="65">
@@ -1719,13 +1719,13 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.142603</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.26131</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.172495</v>
       </c>
     </row>
     <row r="68">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-5.882086</v>
+        <v>-7.061443</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-2.213765</v>
@@ -2356,16 +2356,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0.026982</v>
+        <v>-0.019297</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.074518</v>
+        <v>0.05252</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.408992</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.011952</v>
       </c>
     </row>
     <row r="102">
@@ -2451,16 +2451,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.196526</v>
+        <v>0.150247</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.194156</v>
+        <v>-0.216154</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.168841</v>
+        <v>0.577833</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.872858</v>
+        <v>-0.88481</v>
       </c>
     </row>
     <row r="107">
@@ -6030,7 +6030,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -6280,7 +6284,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -6492,7 +6500,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -7580,7 +7592,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>-7.061443</v>
       </c>
@@ -8200,7 +8216,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="n">
         <v>-0.046279</v>
       </c>
